--- a/output/休暇規程_いいかいご.xlsx
+++ b/output/休暇規程_いいかいご.xlsx
@@ -466,7 +466,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:E133"/>
+  <dimension ref="A1:E146"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="19" customWidth="1" min="1" max="1"/>
@@ -585,267 +585,273 @@
         </is>
       </c>
     </row>
-    <row r="38" ht="20" customHeight="1">
+    <row r="38" ht="32" customHeight="1">
       <c r="A38" s="6" t="inlineStr">
         <is>
-          <t>2　その後も、継続勤務ごとに6か月経過するごとに10日の年次有給休暇を付与する。</t>
-        </is>
-      </c>
-    </row>
-    <row r="39" ht="8" customHeight="1"/>
-    <row r="40" ht="20" customHeight="1">
-      <c r="A40" s="5" t="inlineStr">
+          <t>2　その後は、継続勤務年数に応じ、1年ごとに次の日数を付与する。ただし、直前の1年間の全労働日の8割以上出勤した者に限る。</t>
+        </is>
+      </c>
+    </row>
+    <row r="39" ht="32" customHeight="1">
+      <c r="A39" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">　継続勤務1年6か月：11日　2年6か月：12日　3年6か月：14日　4年6か月：16日　5年6か月：18日　6年6か月以上：20日</t>
+        </is>
+      </c>
+    </row>
+    <row r="40" ht="32" customHeight="1">
+      <c r="A40" s="6" t="inlineStr">
+        <is>
+          <t>3　週所定労働日数が4日以下かつ週所定労働時間が30時間未満の従業員には、労働基準法第39条第3項に定める日数を比例付与する。</t>
+        </is>
+      </c>
+    </row>
+    <row r="41" ht="8" customHeight="1"/>
+    <row r="42" ht="20" customHeight="1">
+      <c r="A42" s="5" t="inlineStr">
         <is>
           <t>（取得方法）</t>
         </is>
       </c>
     </row>
-    <row r="41" ht="32" customHeight="1">
-      <c r="A41" s="6" t="inlineStr">
+    <row r="43" ht="32" customHeight="1">
+      <c r="A43" s="6" t="inlineStr">
         <is>
           <t>第4条　年次有給休暇の取得は、従業員の請求による。会社は業務の正常な運営を妨げる場合を除き、これを認めなければならない。</t>
         </is>
       </c>
     </row>
-    <row r="42" ht="8" customHeight="1"/>
-    <row r="43" ht="20" customHeight="1">
-      <c r="A43" s="5" t="inlineStr">
+    <row r="44" ht="8" customHeight="1"/>
+    <row r="45" ht="20" customHeight="1">
+      <c r="A45" s="5" t="inlineStr">
         <is>
           <t>（時季変更権）</t>
         </is>
       </c>
     </row>
-    <row r="44" ht="20" customHeight="1">
-      <c r="A44" s="6" t="inlineStr">
+    <row r="46" ht="20" customHeight="1">
+      <c r="A46" s="6" t="inlineStr">
         <is>
           <t>第5条　会社は、業務の正常な運営を妨げる場合、休暇の取得時季を変更することができる。</t>
         </is>
       </c>
     </row>
-    <row r="45" ht="8" customHeight="1"/>
-    <row r="46" ht="20" customHeight="1">
-      <c r="A46" s="5" t="inlineStr">
+    <row r="47" ht="8" customHeight="1"/>
+    <row r="48" ht="20" customHeight="1">
+      <c r="A48" s="5" t="inlineStr">
         <is>
           <t>（時間単位年休）</t>
         </is>
       </c>
     </row>
-    <row r="47" ht="32" customHeight="1">
-      <c r="A47" s="6" t="inlineStr">
-        <is>
-          <t>第6条　会社は、労使協定を締結した場合に限り、年次有給休暇の一部を時間単位で取得させることができる。</t>
-        </is>
-      </c>
-    </row>
-    <row r="48" ht="8" customHeight="1"/>
-    <row r="49" ht="20" customHeight="1">
-      <c r="A49" s="5" t="inlineStr">
+    <row r="49" ht="32" customHeight="1">
+      <c r="A49" s="6" t="inlineStr">
+        <is>
+          <t>第6条　会社は、労使協定を締結した場合に限り、年次有給休暇のうち年5日の範囲内で、時間単位で取得させることができる。</t>
+        </is>
+      </c>
+    </row>
+    <row r="50" ht="8" customHeight="1"/>
+    <row r="51" ht="20" customHeight="1">
+      <c r="A51" s="5" t="inlineStr">
         <is>
           <t>（計画的付与）</t>
         </is>
       </c>
     </row>
-    <row r="50" ht="20" customHeight="1">
-      <c r="A50" s="6" t="inlineStr">
+    <row r="52" ht="20" customHeight="1">
+      <c r="A52" s="6" t="inlineStr">
         <is>
           <t>第7条　会社は、労使協定に基づき、年次有給休暇の一部を計画的に付与することができる。</t>
         </is>
       </c>
     </row>
-    <row r="51" ht="8" customHeight="1"/>
-    <row r="52" ht="20" customHeight="1">
-      <c r="A52" s="5" t="inlineStr">
+    <row r="53" ht="8" customHeight="1"/>
+    <row r="54" ht="20" customHeight="1">
+      <c r="A54" s="5" t="inlineStr">
         <is>
           <t>（年5日の取得義務）</t>
         </is>
       </c>
     </row>
-    <row r="53" ht="32" customHeight="1">
-      <c r="A53" s="6" t="inlineStr">
+    <row r="55" ht="32" customHeight="1">
+      <c r="A55" s="6" t="inlineStr">
         <is>
           <t>第8条　会社は、年次有給休暇のうち年間5日については、従業員が必ず取得するよう管理しなければならない。</t>
         </is>
       </c>
     </row>
-    <row r="54" ht="20" customHeight="1">
-      <c r="A54" s="6" t="inlineStr">
+    <row r="56" ht="20" customHeight="1">
+      <c r="A56" s="6" t="inlineStr">
         <is>
           <t>2　従業員が自ら請求しない場合、会社は取得時季を指定して取得させる。</t>
         </is>
       </c>
     </row>
-    <row r="55" ht="8" customHeight="1"/>
-    <row r="56" ht="20" customHeight="1">
-      <c r="A56" s="5" t="inlineStr">
+    <row r="57" ht="8" customHeight="1"/>
+    <row r="58" ht="20" customHeight="1">
+      <c r="A58" s="5" t="inlineStr">
         <is>
           <t>（有効期限）</t>
-        </is>
-      </c>
-    </row>
-    <row r="57" ht="20" customHeight="1">
-      <c r="A57" s="6" t="inlineStr">
-        <is>
-          <t>第9条　年次有給休暇の有効期限は、付与日から2年間とする。</t>
-        </is>
-      </c>
-    </row>
-    <row r="58" ht="20" customHeight="1">
-      <c r="A58" s="6" t="inlineStr">
-        <is>
-          <t>2　繰越は1年間に限り認められるが、2年を経過した分については消滅する。</t>
         </is>
       </c>
     </row>
     <row r="59" ht="20" customHeight="1">
       <c r="A59" s="6" t="inlineStr">
         <is>
+          <t>第9条　年次有給休暇の有効期限は、付与日から2年間とする。</t>
+        </is>
+      </c>
+    </row>
+    <row r="60" ht="20" customHeight="1">
+      <c r="A60" s="6" t="inlineStr">
+        <is>
+          <t>2　繰越は1年間に限り認められるが、2年を経過した分については消滅する。</t>
+        </is>
+      </c>
+    </row>
+    <row r="61" ht="20" customHeight="1">
+      <c r="A61" s="6" t="inlineStr">
+        <is>
           <t>3　消滅した年次有給休暇については、会社は金銭その他の補償を行わない。</t>
         </is>
       </c>
     </row>
-    <row r="60" ht="8" customHeight="1"/>
-    <row r="61" ht="8" customHeight="1">
-      <c r="A61" s="7" t="inlineStr"/>
-      <c r="B61" s="8" t="n"/>
-      <c r="C61" s="8" t="n"/>
-      <c r="D61" s="8" t="n"/>
-      <c r="E61" s="8" t="n"/>
-    </row>
-    <row r="62" ht="10" customHeight="1"/>
-    <row r="63" ht="30" customHeight="1">
-      <c r="A63" s="4" t="inlineStr">
+    <row r="62" ht="8" customHeight="1"/>
+    <row r="63" ht="8" customHeight="1">
+      <c r="A63" s="7" t="inlineStr"/>
+      <c r="B63" s="8" t="n"/>
+      <c r="C63" s="8" t="n"/>
+      <c r="D63" s="8" t="n"/>
+      <c r="E63" s="8" t="n"/>
+    </row>
+    <row r="64" ht="10" customHeight="1"/>
+    <row r="65" ht="30" customHeight="1">
+      <c r="A65" s="4" t="inlineStr">
         <is>
           <t>第3章　特別休暇</t>
         </is>
       </c>
     </row>
-    <row r="64" ht="20" customHeight="1">
-      <c r="A64" s="5" t="inlineStr">
+    <row r="66" ht="20" customHeight="1">
+      <c r="A66" s="5" t="inlineStr">
         <is>
           <t>（慶弔休暇）</t>
-        </is>
-      </c>
-    </row>
-    <row r="65" ht="20" customHeight="1">
-      <c r="A65" s="6" t="inlineStr">
-        <is>
-          <t>第10条　従業員に対し、次の慶弔休暇を付与する。</t>
-        </is>
-      </c>
-    </row>
-    <row r="66" ht="20" customHeight="1">
-      <c r="A66" s="6" t="inlineStr">
-        <is>
-          <t>1　本人の結婚：5日</t>
         </is>
       </c>
     </row>
     <row r="67" ht="20" customHeight="1">
       <c r="A67" s="6" t="inlineStr">
         <is>
-          <t>2　子女の結婚：2日</t>
+          <t>第10条　従業員に対し、次の慶弔休暇を付与する。</t>
         </is>
       </c>
     </row>
     <row r="68" ht="20" customHeight="1">
       <c r="A68" s="6" t="inlineStr">
         <is>
-          <t>3　配偶者の死亡：5日</t>
+          <t>1　本人の結婚：5日</t>
         </is>
       </c>
     </row>
     <row r="69" ht="20" customHeight="1">
       <c r="A69" s="6" t="inlineStr">
         <is>
-          <t>4　父母・子の死亡：5日</t>
+          <t>2　子女の結婚：2日</t>
         </is>
       </c>
     </row>
     <row r="70" ht="20" customHeight="1">
       <c r="A70" s="6" t="inlineStr">
         <is>
-          <t>5　祖父母・兄弟姉妹の死亡：3日</t>
+          <t>3　配偶者の死亡：5日</t>
         </is>
       </c>
     </row>
     <row r="71" ht="20" customHeight="1">
       <c r="A71" s="6" t="inlineStr">
         <is>
-          <t>6　その他会社が必要と認めた場合：別途定める</t>
+          <t>4　父母・子の死亡：5日</t>
         </is>
       </c>
     </row>
     <row r="72" ht="20" customHeight="1">
       <c r="A72" s="6" t="inlineStr">
         <is>
+          <t>5　祖父母・兄弟姉妹の死亡：3日</t>
+        </is>
+      </c>
+    </row>
+    <row r="73" ht="20" customHeight="1">
+      <c r="A73" s="6" t="inlineStr">
+        <is>
+          <t>6　その他会社が必要と認めた場合：別途定める</t>
+        </is>
+      </c>
+    </row>
+    <row r="74" ht="20" customHeight="1">
+      <c r="A74" s="6" t="inlineStr">
+        <is>
           <t>2　慶弔休暇に伴う見舞金・祝い金等は「福利厚生規程」に定める。</t>
         </is>
       </c>
     </row>
-    <row r="73" ht="8" customHeight="1"/>
-    <row r="74" ht="20" customHeight="1">
-      <c r="A74" s="5" t="inlineStr">
+    <row r="75" ht="8" customHeight="1"/>
+    <row r="76" ht="20" customHeight="1">
+      <c r="A76" s="5" t="inlineStr">
         <is>
           <t>（産前産後休業）</t>
         </is>
       </c>
     </row>
-    <row r="75" ht="32" customHeight="1">
-      <c r="A75" s="6" t="inlineStr">
+    <row r="77" ht="32" customHeight="1">
+      <c r="A77" s="6" t="inlineStr">
         <is>
           <t>第11条　従業員が出産する場合は、労働基準法に基づき産前6週間（多胎妊娠の場合は14週間）、産後8週間を休業とする。</t>
         </is>
       </c>
     </row>
-    <row r="76" ht="8" customHeight="1"/>
-    <row r="77" ht="20" customHeight="1">
-      <c r="A77" s="5" t="inlineStr">
+    <row r="78" ht="8" customHeight="1"/>
+    <row r="79" ht="20" customHeight="1">
+      <c r="A79" s="5" t="inlineStr">
         <is>
           <t>（育児休業・介護休業）</t>
         </is>
       </c>
     </row>
-    <row r="78" ht="32" customHeight="1">
-      <c r="A78" s="6" t="inlineStr">
+    <row r="80" ht="32" customHeight="1">
+      <c r="A80" s="6" t="inlineStr">
         <is>
           <t>第12条　従業員は、育児・介護休業法に基づき、育児休業及び介護休業を取得することができる。期間・条件等は同法および「育児・介護休業規程」による。</t>
         </is>
       </c>
     </row>
-    <row r="79" ht="8" customHeight="1"/>
-    <row r="80" ht="20" customHeight="1">
-      <c r="A80" s="5" t="inlineStr">
-        <is>
-          <t>（子の看護休暇・介護休暇）</t>
-        </is>
-      </c>
-    </row>
-    <row r="81" ht="32" customHeight="1">
-      <c r="A81" s="6" t="inlineStr">
-        <is>
-          <t>第13条　従業員は、小学校就学前の子1人につき年間5日（2人以上は10日）の子の看護休暇を取得できる。</t>
-        </is>
-      </c>
-    </row>
+    <row r="81" ht="8" customHeight="1"/>
     <row r="82" ht="20" customHeight="1">
-      <c r="A82" s="6" t="inlineStr">
-        <is>
-          <t>2　要介護家族については、年間5日の介護休暇を取得できる。</t>
-        </is>
-      </c>
-    </row>
-    <row r="83" ht="8" customHeight="1"/>
-    <row r="84" ht="20" customHeight="1">
-      <c r="A84" s="5" t="inlineStr">
-        <is>
-          <t>（病気休暇）</t>
+      <c r="A82" s="5" t="inlineStr">
+        <is>
+          <t>（子の看護等休暇・介護休暇）</t>
+        </is>
+      </c>
+    </row>
+    <row r="83" ht="32" customHeight="1">
+      <c r="A83" s="6" t="inlineStr">
+        <is>
+          <t>第13条　従業員は、小学校第3学年修了までの子を養育する場合、子1人につき年間5日（2人以上は10日）の子の看護等休暇を取得できる。</t>
+        </is>
+      </c>
+    </row>
+    <row r="84" ht="32" customHeight="1">
+      <c r="A84" s="6" t="inlineStr">
+        <is>
+          <t>2　要介護状態にある家族を介護する従業員は、対象家族1人につき年間5日（2人以上は10日）の介護休暇を取得できる。</t>
         </is>
       </c>
     </row>
     <row r="85" ht="32" customHeight="1">
       <c r="A85" s="6" t="inlineStr">
         <is>
-          <t>第14条　従業員が私傷病により就業できない場合は、会社の承認を得て病気休暇を与えることがある。日数や給与の取扱いは「休職規程」による。</t>
+          <t>3　子の看護等休暇及び介護休暇は、1日または時間単位で取得できる。詳細は「育児・介護休業規程」による。</t>
         </is>
       </c>
     </row>
@@ -853,14 +859,14 @@
     <row r="87" ht="20" customHeight="1">
       <c r="A87" s="5" t="inlineStr">
         <is>
-          <t>（公務・公用休暇）</t>
+          <t>（病気休暇）</t>
         </is>
       </c>
     </row>
     <row r="88" ht="32" customHeight="1">
       <c r="A88" s="6" t="inlineStr">
         <is>
-          <t>第15条　従業員が裁判員、証人、選挙、官公庁の要請による職務に従事する場合は、その期間を休暇とする。</t>
+          <t>第14条　従業員が私傷病により就業できない場合は、会社の承認を得て病気休暇を与えることがある。日数や給与の取扱いは「休職規程」による。</t>
         </is>
       </c>
     </row>
@@ -868,14 +874,14 @@
     <row r="90" ht="20" customHeight="1">
       <c r="A90" s="5" t="inlineStr">
         <is>
-          <t>（感染症予防に伴う休暇）</t>
+          <t>（公務・公用休暇）</t>
         </is>
       </c>
     </row>
     <row r="91" ht="32" customHeight="1">
       <c r="A91" s="6" t="inlineStr">
         <is>
-          <t>第16条　従業員が感染症に罹患し、医師の診断や法令に基づき出勤停止とされた場合は、その期間を休暇とする。賃金その他の取扱いは就業規則および賃金規程による。</t>
+          <t>第15条　従業員が裁判員、証人、選挙、官公庁の要請による職務に従事する場合は、その期間を休暇とする。</t>
         </is>
       </c>
     </row>
@@ -883,317 +889,394 @@
     <row r="93" ht="20" customHeight="1">
       <c r="A93" s="5" t="inlineStr">
         <is>
-          <t>（誕生日休暇）</t>
-        </is>
-      </c>
-    </row>
-    <row r="94" ht="20" customHeight="1">
+          <t>（感染症予防に伴う休暇）</t>
+        </is>
+      </c>
+    </row>
+    <row r="94" ht="32" customHeight="1">
       <c r="A94" s="6" t="inlineStr">
         <is>
-          <t>第17条　会社は、従業員に対し、誕生日月に1日の誕生日休暇を付与する。</t>
+          <t>第16条　従業員が感染症に罹患し、医師の診断や法令に基づき出勤停止とされた場合は、その期間を休暇とする。賃金その他の取扱いは就業規則および賃金規程による。</t>
         </is>
       </c>
     </row>
     <row r="95" ht="32" customHeight="1">
       <c r="A95" s="6" t="inlineStr">
         <is>
-          <t>2　シフト勤務等の都合により、従業員の希望がある場合は、誕生日に代えて前後の勤務日に振り替えることができる。</t>
-        </is>
-      </c>
-    </row>
-    <row r="96" ht="20" customHeight="1">
-      <c r="A96" s="6" t="inlineStr">
-        <is>
-          <t>3　誕生日休暇に伴う手当については「福利厚生規程」に定める。</t>
-        </is>
-      </c>
-    </row>
-    <row r="97" ht="8" customHeight="1"/>
-    <row r="98" ht="20" customHeight="1">
-      <c r="A98" s="5" t="inlineStr">
-        <is>
-          <t>（その他の特別休暇）</t>
-        </is>
-      </c>
-    </row>
-    <row r="99" ht="32" customHeight="1">
-      <c r="A99" s="6" t="inlineStr">
-        <is>
-          <t>第18条　会社は、災害その他社会的要請や会社が必要と認める場合に、特別休暇を付与することがある。</t>
-        </is>
-      </c>
-    </row>
-    <row r="100" ht="8" customHeight="1"/>
-    <row r="101" ht="8" customHeight="1">
-      <c r="A101" s="7" t="inlineStr"/>
-      <c r="B101" s="8" t="n"/>
-      <c r="C101" s="8" t="n"/>
-      <c r="D101" s="8" t="n"/>
-      <c r="E101" s="8" t="n"/>
-    </row>
-    <row r="102" ht="10" customHeight="1"/>
-    <row r="103" ht="30" customHeight="1">
-      <c r="A103" s="4" t="inlineStr">
-        <is>
-          <t>第4章　手続</t>
-        </is>
-      </c>
-    </row>
-    <row r="104" ht="20" customHeight="1">
-      <c r="A104" s="5" t="inlineStr">
-        <is>
-          <t>（申請手続）</t>
-        </is>
-      </c>
-    </row>
-    <row r="105" ht="32" customHeight="1">
-      <c r="A105" s="6" t="inlineStr">
-        <is>
-          <t>第19条　従業員は、休暇を取得しようとするときは、所定の様式により事前に申請し、上長の承認を得なければならない。ただし、やむを得ない場合は事後速やかに届け出る。</t>
-        </is>
-      </c>
-    </row>
-    <row r="106" ht="8" customHeight="1"/>
+          <t>2　法令に基づかず、会社の判断により出勤を停止させた場合は、労働基準法第26条に基づき休業手当（平均賃金の100分の60以上）を支払う。</t>
+        </is>
+      </c>
+    </row>
+    <row r="96" ht="8" customHeight="1"/>
+    <row r="97" ht="20" customHeight="1">
+      <c r="A97" s="5" t="inlineStr">
+        <is>
+          <t>（生理休暇）</t>
+        </is>
+      </c>
+    </row>
+    <row r="98" ht="32" customHeight="1">
+      <c r="A98" s="6" t="inlineStr">
+        <is>
+          <t>第16条の2　生理日の就業が著しく困難な女性従業員が請求したときは、必要な期間の休暇を与える。</t>
+        </is>
+      </c>
+    </row>
+    <row r="99" ht="8" customHeight="1"/>
+    <row r="100" ht="20" customHeight="1">
+      <c r="A100" s="5" t="inlineStr">
+        <is>
+          <t>（育児時間）</t>
+        </is>
+      </c>
+    </row>
+    <row r="101" ht="32" customHeight="1">
+      <c r="A101" s="6" t="inlineStr">
+        <is>
+          <t>第16条の3　生後1年に達しない子を育てる女性従業員が請求したときは、休憩時間のほか1日2回、各30分の育児時間を与える。</t>
+        </is>
+      </c>
+    </row>
+    <row r="102" ht="8" customHeight="1"/>
+    <row r="103" ht="20" customHeight="1">
+      <c r="A103" s="5" t="inlineStr">
+        <is>
+          <t>（母性健康管理）</t>
+        </is>
+      </c>
+    </row>
+    <row r="104" ht="32" customHeight="1">
+      <c r="A104" s="6" t="inlineStr">
+        <is>
+          <t>第16条の4　妊娠中及び出産後1年以内の女性従業員が請求したときは、男女雇用機会均等法に基づき、保健指導または健康診査を受けるための時間を与える。</t>
+        </is>
+      </c>
+    </row>
+    <row r="105" ht="8" customHeight="1"/>
+    <row r="106" ht="20" customHeight="1">
+      <c r="A106" s="5" t="inlineStr">
+        <is>
+          <t>（誕生日休暇）</t>
+        </is>
+      </c>
+    </row>
     <row r="107" ht="20" customHeight="1">
-      <c r="A107" s="5" t="inlineStr">
-        <is>
-          <t>（診断書等の提出）</t>
+      <c r="A107" s="6" t="inlineStr">
+        <is>
+          <t>第17条　会社は、従業員に対し、誕生日月に1日の誕生日休暇を付与する。</t>
         </is>
       </c>
     </row>
     <row r="108" ht="32" customHeight="1">
       <c r="A108" s="6" t="inlineStr">
         <is>
-          <t>第20条　従業員は、次の場合に医師の診断書その他会社が認める証明書を提出しなければならない。</t>
+          <t>2　シフト勤務等の都合により、従業員の希望がある場合は、誕生日に代えて前後の勤務日に振り替えることができる。</t>
         </is>
       </c>
     </row>
     <row r="109" ht="20" customHeight="1">
       <c r="A109" s="6" t="inlineStr">
         <is>
+          <t>3　誕生日休暇に伴う手当については「福利厚生規程」に定める。</t>
+        </is>
+      </c>
+    </row>
+    <row r="110" ht="8" customHeight="1"/>
+    <row r="111" ht="20" customHeight="1">
+      <c r="A111" s="5" t="inlineStr">
+        <is>
+          <t>（その他の特別休暇）</t>
+        </is>
+      </c>
+    </row>
+    <row r="112" ht="32" customHeight="1">
+      <c r="A112" s="6" t="inlineStr">
+        <is>
+          <t>第18条　会社は、災害その他社会的要請や会社が必要と認める場合に、特別休暇を付与することがある。</t>
+        </is>
+      </c>
+    </row>
+    <row r="113" ht="8" customHeight="1"/>
+    <row r="114" ht="8" customHeight="1">
+      <c r="A114" s="7" t="inlineStr"/>
+      <c r="B114" s="8" t="n"/>
+      <c r="C114" s="8" t="n"/>
+      <c r="D114" s="8" t="n"/>
+      <c r="E114" s="8" t="n"/>
+    </row>
+    <row r="115" ht="10" customHeight="1"/>
+    <row r="116" ht="30" customHeight="1">
+      <c r="A116" s="4" t="inlineStr">
+        <is>
+          <t>第4章　手続</t>
+        </is>
+      </c>
+    </row>
+    <row r="117" ht="20" customHeight="1">
+      <c r="A117" s="5" t="inlineStr">
+        <is>
+          <t>（申請手続）</t>
+        </is>
+      </c>
+    </row>
+    <row r="118" ht="32" customHeight="1">
+      <c r="A118" s="6" t="inlineStr">
+        <is>
+          <t>第19条　従業員は、休暇を取得しようとするときは、所定の様式により事前に申請し、上長の承認を得なければならない。ただし、やむを得ない場合は事後速やかに届け出る。</t>
+        </is>
+      </c>
+    </row>
+    <row r="119" ht="8" customHeight="1"/>
+    <row r="120" ht="20" customHeight="1">
+      <c r="A120" s="5" t="inlineStr">
+        <is>
+          <t>（診断書等の提出）</t>
+        </is>
+      </c>
+    </row>
+    <row r="121" ht="32" customHeight="1">
+      <c r="A121" s="6" t="inlineStr">
+        <is>
+          <t>第20条　従業員は、次の場合に医師の診断書その他会社が認める証明書を提出しなければならない。</t>
+        </is>
+      </c>
+    </row>
+    <row r="122" ht="20" customHeight="1">
+      <c r="A122" s="6" t="inlineStr">
+        <is>
           <t>1　私傷病により連続して3日以上欠勤するとき</t>
         </is>
       </c>
     </row>
-    <row r="110" ht="20" customHeight="1">
-      <c r="A110" s="6" t="inlineStr">
+    <row r="123" ht="20" customHeight="1">
+      <c r="A123" s="6" t="inlineStr">
         <is>
           <t>2　休職を申請するとき</t>
         </is>
       </c>
     </row>
-    <row r="111" ht="20" customHeight="1">
-      <c r="A111" s="6" t="inlineStr">
+    <row r="124" ht="20" customHeight="1">
+      <c r="A124" s="6" t="inlineStr">
         <is>
           <t>3　復職を希望するとき（精神疾患・適応障害・うつ病等を含む）</t>
         </is>
       </c>
     </row>
-    <row r="112" ht="20" customHeight="1">
-      <c r="A112" s="6" t="inlineStr">
+    <row r="125" ht="20" customHeight="1">
+      <c r="A125" s="6" t="inlineStr">
         <is>
           <t>4　産前産後休業、育児休業、介護休業、感染症罹患など、法令に基づく休暇を取得するとき</t>
         </is>
       </c>
     </row>
-    <row r="113" ht="20" customHeight="1">
-      <c r="A113" s="6" t="inlineStr">
+    <row r="126" ht="20" customHeight="1">
+      <c r="A126" s="6" t="inlineStr">
         <is>
           <t>5　会社が安全衛生管理上必要と認めたとき</t>
         </is>
       </c>
     </row>
-    <row r="114" ht="20" customHeight="1">
-      <c r="A114" s="6" t="inlineStr">
+    <row r="127" ht="20" customHeight="1">
+      <c r="A127" s="6" t="inlineStr">
         <is>
           <t>2　診断書等の作成費用は、原則として従業員の負担とする。</t>
         </is>
       </c>
     </row>
-    <row r="115" ht="20" customHeight="1">
-      <c r="A115" s="6" t="inlineStr">
+    <row r="128" ht="20" customHeight="1">
+      <c r="A128" s="6" t="inlineStr">
         <is>
           <t>3　ただし、次の各号に該当する場合は会社が費用を負担する。</t>
         </is>
       </c>
     </row>
-    <row r="116" ht="20" customHeight="1">
-      <c r="A116" s="6" t="inlineStr">
+    <row r="129" ht="20" customHeight="1">
+      <c r="A129" s="6" t="inlineStr">
         <is>
           <t xml:space="preserve">　1　会社が独自に必要と判断し、従業員の申請とは別に診断書その他の証明書を求めた場合</t>
         </is>
       </c>
     </row>
-    <row r="117" ht="20" customHeight="1">
-      <c r="A117" s="6" t="inlineStr">
+    <row r="130" ht="20" customHeight="1">
+      <c r="A130" s="6" t="inlineStr">
         <is>
           <t xml:space="preserve">　2　労働安全衛生法に基づく健康診断や再検査、特殊健康診断に関する場合</t>
         </is>
       </c>
     </row>
-    <row r="118" ht="20" customHeight="1">
-      <c r="A118" s="6" t="inlineStr">
+    <row r="131" ht="20" customHeight="1">
+      <c r="A131" s="6" t="inlineStr">
         <is>
           <t xml:space="preserve">　3　労災（業務災害・通勤災害）に関する診断書の場合</t>
         </is>
       </c>
     </row>
-    <row r="119" ht="8" customHeight="1"/>
-    <row r="120" ht="8" customHeight="1">
-      <c r="A120" s="7" t="inlineStr"/>
-      <c r="B120" s="8" t="n"/>
-      <c r="C120" s="8" t="n"/>
-      <c r="D120" s="8" t="n"/>
-      <c r="E120" s="8" t="n"/>
-    </row>
-    <row r="121" ht="10" customHeight="1"/>
-    <row r="122" ht="30" customHeight="1">
-      <c r="A122" s="4" t="inlineStr">
+    <row r="132" ht="8" customHeight="1"/>
+    <row r="133" ht="8" customHeight="1">
+      <c r="A133" s="7" t="inlineStr"/>
+      <c r="B133" s="8" t="n"/>
+      <c r="C133" s="8" t="n"/>
+      <c r="D133" s="8" t="n"/>
+      <c r="E133" s="8" t="n"/>
+    </row>
+    <row r="134" ht="10" customHeight="1"/>
+    <row r="135" ht="30" customHeight="1">
+      <c r="A135" s="4" t="inlineStr">
         <is>
           <t>第5章　その他</t>
         </is>
       </c>
     </row>
-    <row r="123" ht="20" customHeight="1">
-      <c r="A123" s="5" t="inlineStr">
+    <row r="136" ht="20" customHeight="1">
+      <c r="A136" s="5" t="inlineStr">
         <is>
           <t>（不利益取扱い禁止）</t>
         </is>
       </c>
     </row>
-    <row r="124" ht="32" customHeight="1">
-      <c r="A124" s="6" t="inlineStr">
+    <row r="137" ht="32" customHeight="1">
+      <c r="A137" s="6" t="inlineStr">
         <is>
           <t>第21条　会社は、従業員が法令に基づく休暇または本規程による休暇を取得したことを理由として、不利益取扱いをしてはならない。</t>
         </is>
       </c>
     </row>
-    <row r="125" ht="8" customHeight="1"/>
-    <row r="126" ht="20" customHeight="1">
-      <c r="A126" s="5" t="inlineStr">
+    <row r="138" ht="8" customHeight="1"/>
+    <row r="139" ht="20" customHeight="1">
+      <c r="A139" s="5" t="inlineStr">
         <is>
           <t>（休暇中の待遇）</t>
         </is>
       </c>
     </row>
-    <row r="127" ht="32" customHeight="1">
-      <c r="A127" s="6" t="inlineStr">
+    <row r="140" ht="32" customHeight="1">
+      <c r="A140" s="6" t="inlineStr">
         <is>
           <t>第22条　休暇中の賃金、社会保険その他の待遇については、就業規則、賃金規程及び関係規程による。</t>
         </is>
       </c>
     </row>
-    <row r="128" ht="8" customHeight="1"/>
-    <row r="129" ht="8" customHeight="1">
-      <c r="A129" s="7" t="inlineStr"/>
-      <c r="B129" s="8" t="n"/>
-      <c r="C129" s="8" t="n"/>
-      <c r="D129" s="8" t="n"/>
-      <c r="E129" s="8" t="n"/>
-    </row>
-    <row r="130" ht="10" customHeight="1"/>
-    <row r="131" ht="30" customHeight="1">
-      <c r="A131" s="4" t="inlineStr">
+    <row r="141" ht="8" customHeight="1"/>
+    <row r="142" ht="8" customHeight="1">
+      <c r="A142" s="7" t="inlineStr"/>
+      <c r="B142" s="8" t="n"/>
+      <c r="C142" s="8" t="n"/>
+      <c r="D142" s="8" t="n"/>
+      <c r="E142" s="8" t="n"/>
+    </row>
+    <row r="143" ht="10" customHeight="1"/>
+    <row r="144" ht="30" customHeight="1">
+      <c r="A144" s="4" t="inlineStr">
         <is>
           <t>附則</t>
         </is>
       </c>
     </row>
-    <row r="132" ht="20" customHeight="1">
-      <c r="A132" s="6" t="inlineStr">
+    <row r="145" ht="20" customHeight="1">
+      <c r="A145" s="6" t="inlineStr">
         <is>
           <t>1　本規程に定めのない事項は、就業規則その他関係規程による。</t>
         </is>
       </c>
     </row>
-    <row r="133" ht="20" customHeight="1">
-      <c r="A133" s="6" t="inlineStr">
+    <row r="146" ht="20" customHeight="1">
+      <c r="A146" s="6" t="inlineStr">
         <is>
           <t>2　本規程は令和8年2月1日から施行する。</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="84">
+  <mergeCells count="94">
+    <mergeCell ref="A39:E39"/>
+    <mergeCell ref="A48:E48"/>
+    <mergeCell ref="A142:E142"/>
     <mergeCell ref="A1:E1"/>
+    <mergeCell ref="A45:E45"/>
     <mergeCell ref="A94:E94"/>
     <mergeCell ref="A103:E103"/>
+    <mergeCell ref="A79:E79"/>
     <mergeCell ref="A87:E87"/>
     <mergeCell ref="A65:E65"/>
+    <mergeCell ref="A128:E128"/>
+    <mergeCell ref="A137:E137"/>
     <mergeCell ref="A37:E37"/>
     <mergeCell ref="A46:E46"/>
-    <mergeCell ref="A105:E105"/>
+    <mergeCell ref="A136:E136"/>
     <mergeCell ref="A26:E26"/>
-    <mergeCell ref="A57:E57"/>
-    <mergeCell ref="A113:E113"/>
+    <mergeCell ref="A139:E139"/>
     <mergeCell ref="A71:E71"/>
     <mergeCell ref="A129:E129"/>
     <mergeCell ref="A91:E91"/>
     <mergeCell ref="A131:E131"/>
+    <mergeCell ref="A100:E100"/>
     <mergeCell ref="A43:E43"/>
     <mergeCell ref="A52:E52"/>
     <mergeCell ref="A63:E63"/>
-    <mergeCell ref="A115:E115"/>
     <mergeCell ref="A93:E93"/>
+    <mergeCell ref="A130:E130"/>
     <mergeCell ref="A77:E77"/>
+    <mergeCell ref="A83:E83"/>
     <mergeCell ref="A49:E49"/>
-    <mergeCell ref="A132:E132"/>
     <mergeCell ref="A36:E36"/>
     <mergeCell ref="A69:E69"/>
-    <mergeCell ref="A78:E78"/>
     <mergeCell ref="A118:E118"/>
-    <mergeCell ref="A75:E75"/>
     <mergeCell ref="A133:E133"/>
     <mergeCell ref="A80:E80"/>
     <mergeCell ref="A120:E120"/>
+    <mergeCell ref="A55:E55"/>
     <mergeCell ref="A95:E95"/>
     <mergeCell ref="A104:E104"/>
-    <mergeCell ref="A81:E81"/>
+    <mergeCell ref="A97:E97"/>
+    <mergeCell ref="A106:E106"/>
     <mergeCell ref="A38:E38"/>
-    <mergeCell ref="A96:E96"/>
     <mergeCell ref="A31:E31"/>
     <mergeCell ref="A58:E58"/>
     <mergeCell ref="A40:E40"/>
     <mergeCell ref="A67:E67"/>
+    <mergeCell ref="A73:E73"/>
     <mergeCell ref="A82:E82"/>
+    <mergeCell ref="A60:E60"/>
     <mergeCell ref="A123:E123"/>
-    <mergeCell ref="A110:E110"/>
+    <mergeCell ref="A146:E146"/>
     <mergeCell ref="A124:E124"/>
     <mergeCell ref="A25:E25"/>
     <mergeCell ref="A108:E108"/>
     <mergeCell ref="A84:E84"/>
     <mergeCell ref="A66:E66"/>
-    <mergeCell ref="A50:E50"/>
-    <mergeCell ref="A47:E47"/>
+    <mergeCell ref="A42:E42"/>
+    <mergeCell ref="A135:E135"/>
+    <mergeCell ref="A144:E144"/>
     <mergeCell ref="A122:E122"/>
+    <mergeCell ref="A125:E125"/>
     <mergeCell ref="A72:E72"/>
     <mergeCell ref="A28:E28"/>
     <mergeCell ref="A112:E112"/>
+    <mergeCell ref="A121:E121"/>
     <mergeCell ref="A13:E13"/>
-    <mergeCell ref="A44:E44"/>
     <mergeCell ref="A127:E127"/>
     <mergeCell ref="A30:E30"/>
     <mergeCell ref="A114:E114"/>
     <mergeCell ref="A59:E59"/>
-    <mergeCell ref="A64:E64"/>
     <mergeCell ref="A98:E98"/>
+    <mergeCell ref="A51:E51"/>
     <mergeCell ref="A107:E107"/>
     <mergeCell ref="A61:E61"/>
     <mergeCell ref="A88:E88"/>
     <mergeCell ref="A70:E70"/>
     <mergeCell ref="A54:E54"/>
-    <mergeCell ref="A41:E41"/>
     <mergeCell ref="A90:E90"/>
-    <mergeCell ref="A99:E99"/>
     <mergeCell ref="A74:E74"/>
     <mergeCell ref="A56:E56"/>
     <mergeCell ref="A27:E27"/>
+    <mergeCell ref="A145:E145"/>
     <mergeCell ref="A101:E101"/>
+    <mergeCell ref="A76:E76"/>
     <mergeCell ref="A33:E33"/>
     <mergeCell ref="A85:E85"/>
     <mergeCell ref="A116:E116"/>
     <mergeCell ref="A126:E126"/>
-    <mergeCell ref="A53:E53"/>
+    <mergeCell ref="A140:E140"/>
     <mergeCell ref="A109:E109"/>
     <mergeCell ref="A35:E35"/>
     <mergeCell ref="A68:E68"/>
